--- a/rules/CORE-000744/positive/04/data/unit-test-coreid-CG0174_EX_FA_positive_one_one.xlsx
+++ b/rules/CORE-000744/positive/04/data/unit-test-coreid-CG0174_EX_FA_positive_one_one.xlsx
@@ -867,7 +867,11 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="M3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Num</t>
@@ -888,7 +892,11 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="R3" s="3" t="n"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
           <t>Num</t>
@@ -1722,7 +1730,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
+          <t>ABC123</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1749,7 +1757,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
+          <t>ABC123</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1776,7 +1784,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
+          <t>ABC123</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1803,7 +1811,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
+          <t>ABC123</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1830,7 +1838,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
+          <t>ABC123</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -1859,7 +1867,7 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
+          <t>ABC123</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
